--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/19,10,26 Останкино КИ и ЗПФ/дв 19,10,26 млрсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/19,10,26 Останкино КИ и ЗПФ/дв 19,10,26 млрсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\19,10,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2428C2C-F1D9-4383-AD5A-BAD279328797}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC48ACD-F496-4BB6-AE95-8FD9DC124178}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AG$107</definedName>
   </definedNames>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -5884,7 +5884,10 @@
       </c>
       <c r="AF4" s="1"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="20"/>
+      <c r="AH4" s="20">
+        <f>6*AH5</f>
+        <v>4820.2200000000012</v>
+      </c>
       <c r="AI4" s="1"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="1"/>
@@ -6002,7 +6005,10 @@
         <f>SUM(AG6:AG496)</f>
         <v>5801.88</v>
       </c>
-      <c r="AH5" s="20"/>
+      <c r="AH5" s="4">
+        <f>SUM(AH6:AH496)</f>
+        <v>803.37000000000023</v>
+      </c>
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="1"/>
@@ -6116,7 +6122,10 @@
         <f>G6*R6</f>
         <v>0</v>
       </c>
-      <c r="AH6" s="20"/>
+      <c r="AH6" s="20">
+        <f>P6*G6</f>
+        <v>3.1408</v>
+      </c>
       <c r="AI6" s="1"/>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="1"/>
@@ -6234,7 +6243,10 @@
         <f t="shared" ref="AG7:AG70" si="7">G7*R7</f>
         <v>100</v>
       </c>
-      <c r="AH7" s="20"/>
+      <c r="AH7" s="20">
+        <f t="shared" ref="AH7:AH70" si="8">P7*G7</f>
+        <v>11.68</v>
+      </c>
       <c r="AI7" s="1"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="1"/>
@@ -6351,7 +6363,10 @@
         <f t="shared" si="7"/>
         <v>75</v>
       </c>
-      <c r="AH8" s="20"/>
+      <c r="AH8" s="20">
+        <f t="shared" si="8"/>
+        <v>7.3176000000000005</v>
+      </c>
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="1"/>
@@ -6419,7 +6434,7 @@
         <v>266</v>
       </c>
       <c r="R9" s="5">
-        <f t="shared" ref="R8:R16" si="8">S9</f>
+        <f t="shared" ref="R9:R16" si="9">S9</f>
         <v>350</v>
       </c>
       <c r="S9" s="22">
@@ -6469,7 +6484,10 @@
         <f t="shared" si="7"/>
         <v>87.5</v>
       </c>
-      <c r="AH9" s="20"/>
+      <c r="AH9" s="20">
+        <f t="shared" si="8"/>
+        <v>8.9</v>
+      </c>
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
@@ -6586,7 +6604,10 @@
         <f t="shared" si="7"/>
         <v>110</v>
       </c>
-      <c r="AH10" s="20"/>
+      <c r="AH10" s="20">
+        <f t="shared" si="8"/>
+        <v>29.959399999999999</v>
+      </c>
       <c r="AI10" s="1"/>
       <c r="AJ10" s="1"/>
       <c r="AK10" s="1"/>
@@ -6703,7 +6724,10 @@
         <f t="shared" si="7"/>
         <v>65</v>
       </c>
-      <c r="AH11" s="20"/>
+      <c r="AH11" s="20">
+        <f t="shared" si="8"/>
+        <v>6.8989999999999991</v>
+      </c>
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
@@ -6820,7 +6844,10 @@
         <f t="shared" si="7"/>
         <v>35</v>
       </c>
-      <c r="AH12" s="20"/>
+      <c r="AH12" s="20">
+        <f t="shared" si="8"/>
+        <v>4.8369999999999997</v>
+      </c>
       <c r="AI12" s="1"/>
       <c r="AJ12" s="1"/>
       <c r="AK12" s="1"/>
@@ -6888,7 +6915,7 @@
         <v>30.370000000000033</v>
       </c>
       <c r="R13" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>150</v>
       </c>
       <c r="S13" s="22">
@@ -6938,7 +6965,10 @@
         <f t="shared" si="7"/>
         <v>150</v>
       </c>
-      <c r="AH13" s="20"/>
+      <c r="AH13" s="20">
+        <f t="shared" si="8"/>
+        <v>24.155000000000001</v>
+      </c>
       <c r="AI13" s="1"/>
       <c r="AJ13" s="1"/>
       <c r="AK13" s="1"/>
@@ -7055,7 +7085,10 @@
         <f t="shared" si="7"/>
         <v>65</v>
       </c>
-      <c r="AH14" s="20"/>
+      <c r="AH14" s="20">
+        <f t="shared" si="8"/>
+        <v>5.55</v>
+      </c>
       <c r="AI14" s="1"/>
       <c r="AJ14" s="1"/>
       <c r="AK14" s="1"/>
@@ -7172,7 +7205,10 @@
         <f t="shared" si="7"/>
         <v>80</v>
       </c>
-      <c r="AH15" s="20"/>
+      <c r="AH15" s="20">
+        <f t="shared" si="8"/>
+        <v>5.4889999999999999</v>
+      </c>
       <c r="AI15" s="1"/>
       <c r="AJ15" s="1"/>
       <c r="AK15" s="1"/>
@@ -7240,7 +7276,7 @@
         <v>227</v>
       </c>
       <c r="R16" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>350</v>
       </c>
       <c r="S16" s="22">
@@ -7290,7 +7326,10 @@
         <f t="shared" si="7"/>
         <v>87.5</v>
       </c>
-      <c r="AH16" s="20"/>
+      <c r="AH16" s="20">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
       <c r="AI16" s="1"/>
       <c r="AJ16" s="1"/>
       <c r="AK16" s="1"/>
@@ -7355,7 +7394,7 @@
       </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="5">
-        <f t="shared" ref="R7:R70" si="9">ROUND(Q17,0)</f>
+        <f t="shared" ref="R17:R68" si="10">ROUND(Q17,0)</f>
         <v>0</v>
       </c>
       <c r="S17" s="22"/>
@@ -7402,7 +7441,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH17" s="20"/>
+      <c r="AH17" s="20">
+        <f t="shared" si="8"/>
+        <v>1.6</v>
+      </c>
       <c r="AI17" s="1"/>
       <c r="AJ17" s="1"/>
       <c r="AK17" s="1"/>
@@ -7519,7 +7561,10 @@
         <f t="shared" si="7"/>
         <v>500</v>
       </c>
-      <c r="AH18" s="20"/>
+      <c r="AH18" s="20">
+        <f t="shared" si="8"/>
+        <v>52.965599999999995</v>
+      </c>
       <c r="AI18" s="1"/>
       <c r="AJ18" s="1"/>
       <c r="AK18" s="1"/>
@@ -7584,7 +7629,7 @@
       </c>
       <c r="Q19" s="14"/>
       <c r="R19" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="S19" s="22"/>
@@ -7633,7 +7678,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH19" s="20"/>
+      <c r="AH19" s="20">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AI19" s="1"/>
       <c r="AJ19" s="1"/>
       <c r="AK19" s="1"/>
@@ -7747,7 +7795,10 @@
         <f t="shared" si="7"/>
         <v>80</v>
       </c>
-      <c r="AH20" s="20"/>
+      <c r="AH20" s="20">
+        <f t="shared" si="8"/>
+        <v>0.32000000000000006</v>
+      </c>
       <c r="AI20" s="1"/>
       <c r="AJ20" s="1"/>
       <c r="AK20" s="1"/>
@@ -7864,7 +7915,10 @@
         <f t="shared" si="7"/>
         <v>260</v>
       </c>
-      <c r="AH21" s="20"/>
+      <c r="AH21" s="20">
+        <f t="shared" si="8"/>
+        <v>20.309000000000001</v>
+      </c>
       <c r="AI21" s="1"/>
       <c r="AJ21" s="1"/>
       <c r="AK21" s="1"/>
@@ -7980,7 +8034,10 @@
         <f t="shared" si="7"/>
         <v>33</v>
       </c>
-      <c r="AH22" s="20"/>
+      <c r="AH22" s="20">
+        <f t="shared" si="8"/>
+        <v>1.3640000000000001</v>
+      </c>
       <c r="AI22" s="1"/>
       <c r="AJ22" s="1"/>
       <c r="AK22" s="1"/>
@@ -8097,7 +8154,10 @@
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="AH23" s="20"/>
+      <c r="AH23" s="20">
+        <f t="shared" si="8"/>
+        <v>3.7171999999999996</v>
+      </c>
       <c r="AI23" s="1"/>
       <c r="AJ23" s="1"/>
       <c r="AK23" s="1"/>
@@ -8211,7 +8271,10 @@
         <f t="shared" si="7"/>
         <v>60</v>
       </c>
-      <c r="AH24" s="20"/>
+      <c r="AH24" s="20">
+        <f t="shared" si="8"/>
+        <v>1.9088000000000001</v>
+      </c>
       <c r="AI24" s="1"/>
       <c r="AJ24" s="1"/>
       <c r="AK24" s="1"/>
@@ -8325,7 +8388,10 @@
         <f t="shared" si="7"/>
         <v>3.5999999999999996</v>
       </c>
-      <c r="AH25" s="20"/>
+      <c r="AH25" s="20">
+        <f t="shared" si="8"/>
+        <v>0.73799999999999988</v>
+      </c>
       <c r="AI25" s="1"/>
       <c r="AJ25" s="1"/>
       <c r="AK25" s="1"/>
@@ -8389,7 +8455,7 @@
         <v>5.8</v>
       </c>
       <c r="Q26" s="5">
-        <f t="shared" ref="Q26:Q40" si="10">15*P26-O26-F26</f>
+        <f t="shared" ref="Q26:Q40" si="11">15*P26-O26-F26</f>
         <v>38</v>
       </c>
       <c r="R26" s="5">
@@ -8444,7 +8510,10 @@
         <f t="shared" si="7"/>
         <v>7.1999999999999993</v>
       </c>
-      <c r="AH26" s="20"/>
+      <c r="AH26" s="20">
+        <f t="shared" si="8"/>
+        <v>0.52200000000000002</v>
+      </c>
       <c r="AI26" s="1"/>
       <c r="AJ26" s="1"/>
       <c r="AK26" s="1"/>
@@ -8512,7 +8581,7 @@
         <v>218.79999999999995</v>
       </c>
       <c r="R27" s="5">
-        <f t="shared" ref="R20:R40" si="11">S27</f>
+        <f t="shared" ref="R27:R40" si="12">S27</f>
         <v>350</v>
       </c>
       <c r="S27" s="22">
@@ -8564,7 +8633,10 @@
         <f t="shared" si="7"/>
         <v>52.5</v>
       </c>
-      <c r="AH27" s="20"/>
+      <c r="AH27" s="20">
+        <f t="shared" si="8"/>
+        <v>3.51</v>
+      </c>
       <c r="AI27" s="1"/>
       <c r="AJ27" s="1"/>
       <c r="AK27" s="1"/>
@@ -8628,11 +8700,11 @@
         <v>65.474400000000003</v>
       </c>
       <c r="Q28" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>25.72</v>
       </c>
       <c r="R28" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>150</v>
       </c>
       <c r="S28" s="22">
@@ -8682,7 +8754,10 @@
         <f t="shared" si="7"/>
         <v>150</v>
       </c>
-      <c r="AH28" s="20"/>
+      <c r="AH28" s="20">
+        <f t="shared" si="8"/>
+        <v>65.474400000000003</v>
+      </c>
       <c r="AI28" s="1"/>
       <c r="AJ28" s="1"/>
       <c r="AK28" s="1"/>
@@ -8798,7 +8873,10 @@
         <f t="shared" si="7"/>
         <v>6.4</v>
       </c>
-      <c r="AH29" s="20"/>
+      <c r="AH29" s="20">
+        <f t="shared" si="8"/>
+        <v>1.7600000000000002</v>
+      </c>
       <c r="AI29" s="1"/>
       <c r="AJ29" s="1"/>
       <c r="AK29" s="1"/>
@@ -8862,7 +8940,7 @@
         <v>32</v>
       </c>
       <c r="Q30" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>70</v>
       </c>
       <c r="R30" s="5">
@@ -8915,7 +8993,10 @@
         <f t="shared" si="7"/>
         <v>68</v>
       </c>
-      <c r="AH30" s="20"/>
+      <c r="AH30" s="20">
+        <f t="shared" si="8"/>
+        <v>12.8</v>
+      </c>
       <c r="AI30" s="1"/>
       <c r="AJ30" s="1"/>
       <c r="AK30" s="1"/>
@@ -9029,7 +9110,10 @@
         <f t="shared" si="7"/>
         <v>40</v>
       </c>
-      <c r="AH31" s="20"/>
+      <c r="AH31" s="20">
+        <f t="shared" si="8"/>
+        <v>9.5200000000000014</v>
+      </c>
       <c r="AI31" s="1"/>
       <c r="AJ31" s="1"/>
       <c r="AK31" s="1"/>
@@ -9143,7 +9227,10 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="AH32" s="20"/>
+      <c r="AH32" s="20">
+        <f t="shared" si="8"/>
+        <v>0.89999999999999991</v>
+      </c>
       <c r="AI32" s="1"/>
       <c r="AJ32" s="1"/>
       <c r="AK32" s="1"/>
@@ -9207,7 +9294,7 @@
         <v>11.065000000000001</v>
       </c>
       <c r="Q33" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>20.052000000000021</v>
       </c>
       <c r="R33" s="5">
@@ -9260,7 +9347,10 @@
         <f t="shared" si="7"/>
         <v>70</v>
       </c>
-      <c r="AH33" s="20"/>
+      <c r="AH33" s="20">
+        <f t="shared" si="8"/>
+        <v>11.065000000000001</v>
+      </c>
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
       <c r="AK33" s="1"/>
@@ -9376,7 +9466,10 @@
         <f t="shared" si="7"/>
         <v>40</v>
       </c>
-      <c r="AH34" s="20"/>
+      <c r="AH34" s="20">
+        <f t="shared" si="8"/>
+        <v>9.9456000000000007</v>
+      </c>
       <c r="AI34" s="1"/>
       <c r="AJ34" s="1"/>
       <c r="AK34" s="1"/>
@@ -9440,7 +9533,7 @@
         <v>6.1970000000000001</v>
       </c>
       <c r="Q35" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>26.576000000000001</v>
       </c>
       <c r="R35" s="5">
@@ -9493,7 +9586,10 @@
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="AH35" s="20"/>
+      <c r="AH35" s="20">
+        <f t="shared" si="8"/>
+        <v>6.1970000000000001</v>
+      </c>
       <c r="AI35" s="1"/>
       <c r="AJ35" s="1"/>
       <c r="AK35" s="1"/>
@@ -9557,7 +9653,7 @@
         <v>14.0786</v>
       </c>
       <c r="Q36" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>56.757999999999996</v>
       </c>
       <c r="R36" s="5">
@@ -9610,7 +9706,10 @@
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="AH36" s="20"/>
+      <c r="AH36" s="20">
+        <f t="shared" si="8"/>
+        <v>14.0786</v>
+      </c>
       <c r="AI36" s="1"/>
       <c r="AJ36" s="1"/>
       <c r="AK36" s="1"/>
@@ -9724,7 +9823,10 @@
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
-      <c r="AH37" s="20"/>
+      <c r="AH37" s="20">
+        <f t="shared" si="8"/>
+        <v>9.42</v>
+      </c>
       <c r="AI37" s="1"/>
       <c r="AJ37" s="1"/>
       <c r="AK37" s="1"/>
@@ -9771,7 +9873,7 @@
         <v>3.3</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="12">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="13">E38-K38</f>
         <v>-3.3</v>
       </c>
       <c r="M38" s="1"/>
@@ -9780,12 +9882,12 @@
         <v>10</v>
       </c>
       <c r="P38" s="1">
-        <f t="shared" ref="P38:P69" si="13">E38/5</f>
+        <f t="shared" ref="P38:P69" si="14">E38/5</f>
         <v>0</v>
       </c>
       <c r="Q38" s="5"/>
       <c r="R38" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>50</v>
       </c>
       <c r="S38" s="22">
@@ -9797,7 +9899,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U38" s="1" t="e">
-        <f t="shared" ref="U38:U69" si="14">(F38+O38)/P38</f>
+        <f t="shared" ref="U38:U69" si="15">(F38+O38)/P38</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V38" s="1">
@@ -9837,7 +9939,10 @@
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="AH38" s="20"/>
+      <c r="AH38" s="20">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AI38" s="1"/>
       <c r="AJ38" s="1"/>
       <c r="AK38" s="1"/>
@@ -9888,7 +9993,7 @@
         <v>49.5</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-5.2379999999999995</v>
       </c>
       <c r="M39" s="1"/>
@@ -9897,7 +10002,7 @@
         <v>80</v>
       </c>
       <c r="P39" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.8523999999999994</v>
       </c>
       <c r="Q39" s="5"/>
@@ -9913,7 +10018,7 @@
         <v>19.078216076996071</v>
       </c>
       <c r="U39" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15.689304595363971</v>
       </c>
       <c r="V39" s="1">
@@ -9951,7 +10056,10 @@
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="AH39" s="20"/>
+      <c r="AH39" s="20">
+        <f t="shared" si="8"/>
+        <v>8.8523999999999994</v>
+      </c>
       <c r="AI39" s="1"/>
       <c r="AJ39" s="1"/>
       <c r="AK39" s="1"/>
@@ -10002,7 +10110,7 @@
         <v>428.5</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-88.5</v>
       </c>
       <c r="M40" s="1"/>
@@ -10011,15 +10119,15 @@
         <v>450</v>
       </c>
       <c r="P40" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>68</v>
       </c>
       <c r="Q40" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>306</v>
       </c>
       <c r="R40" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>500</v>
       </c>
       <c r="S40" s="22">
@@ -10031,7 +10139,7 @@
         <v>17.852941176470587</v>
       </c>
       <c r="U40" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.5</v>
       </c>
       <c r="V40" s="1">
@@ -10069,7 +10177,10 @@
         <f t="shared" si="7"/>
         <v>175</v>
       </c>
-      <c r="AH40" s="20"/>
+      <c r="AH40" s="20">
+        <f t="shared" si="8"/>
+        <v>23.799999999999997</v>
+      </c>
       <c r="AI40" s="1"/>
       <c r="AJ40" s="1"/>
       <c r="AK40" s="1"/>
@@ -10120,7 +10231,7 @@
         <v>59</v>
       </c>
       <c r="L41" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-63</v>
       </c>
       <c r="M41" s="11"/>
@@ -10129,12 +10240,12 @@
         <v>0</v>
       </c>
       <c r="P41" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-0.8</v>
       </c>
       <c r="Q41" s="14"/>
       <c r="R41" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="S41" s="22"/>
@@ -10143,7 +10254,7 @@
         <v>0</v>
       </c>
       <c r="U41" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V41" s="11">
@@ -10183,7 +10294,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH41" s="20"/>
+      <c r="AH41" s="20">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AI41" s="1"/>
       <c r="AJ41" s="1"/>
       <c r="AK41" s="1"/>
@@ -10234,7 +10348,7 @@
         <v>100</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-21</v>
       </c>
       <c r="M42" s="1"/>
@@ -10243,7 +10357,7 @@
         <v>170</v>
       </c>
       <c r="P42" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>15.8</v>
       </c>
       <c r="Q42" s="5"/>
@@ -10259,7 +10373,7 @@
         <v>20.379746835443036</v>
       </c>
       <c r="U42" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>18.481012658227847</v>
       </c>
       <c r="V42" s="1">
@@ -10299,7 +10413,10 @@
         <f t="shared" si="7"/>
         <v>12.299999999999999</v>
       </c>
-      <c r="AH42" s="20"/>
+      <c r="AH42" s="20">
+        <f t="shared" si="8"/>
+        <v>6.4779999999999998</v>
+      </c>
       <c r="AI42" s="1"/>
       <c r="AJ42" s="1"/>
       <c r="AK42" s="1"/>
@@ -10346,7 +10463,7 @@
         <v>1</v>
       </c>
       <c r="L43" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.499999999999992E-2</v>
       </c>
       <c r="M43" s="11"/>
@@ -10355,12 +10472,12 @@
         <v>0</v>
       </c>
       <c r="P43" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.20699999999999999</v>
       </c>
       <c r="Q43" s="14"/>
       <c r="R43" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="S43" s="22"/>
@@ -10369,7 +10486,7 @@
         <v>236.87922705314011</v>
       </c>
       <c r="U43" s="11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>236.87922705314011</v>
       </c>
       <c r="V43" s="11">
@@ -10407,7 +10524,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH43" s="20"/>
+      <c r="AH43" s="20">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AI43" s="1"/>
       <c r="AJ43" s="1"/>
       <c r="AK43" s="1"/>
@@ -10458,7 +10578,7 @@
         <v>133</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-28</v>
       </c>
       <c r="M44" s="1"/>
@@ -10467,11 +10587,11 @@
         <v>200</v>
       </c>
       <c r="P44" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>21</v>
       </c>
       <c r="Q44" s="5">
-        <f t="shared" ref="Q44:Q48" si="15">15*P44-O44-F44</f>
+        <f t="shared" ref="Q44:Q48" si="16">15*P44-O44-F44</f>
         <v>112</v>
       </c>
       <c r="R44" s="5">
@@ -10486,7 +10606,7 @@
         <v>19.666666666666668</v>
       </c>
       <c r="U44" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.6666666666666661</v>
       </c>
       <c r="V44" s="1">
@@ -10525,8 +10645,8 @@
         <v>75.599999999999994</v>
       </c>
       <c r="AH44" s="20">
-        <f>V44/W44</f>
-        <v>1.5483870967741935</v>
+        <f t="shared" si="8"/>
+        <v>7.56</v>
       </c>
       <c r="AI44" s="1"/>
       <c r="AJ44" s="1"/>
@@ -10578,7 +10698,7 @@
         <v>39</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-4</v>
       </c>
       <c r="M45" s="1"/>
@@ -10587,11 +10707,11 @@
         <v>8</v>
       </c>
       <c r="P45" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7</v>
       </c>
       <c r="Q45" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>53</v>
       </c>
       <c r="R45" s="5">
@@ -10606,7 +10726,7 @@
         <v>20.285714285714285</v>
       </c>
       <c r="U45" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.4285714285714288</v>
       </c>
       <c r="V45" s="1">
@@ -10646,7 +10766,10 @@
         <f t="shared" si="7"/>
         <v>29.700000000000003</v>
       </c>
-      <c r="AH45" s="20"/>
+      <c r="AH45" s="20">
+        <f t="shared" si="8"/>
+        <v>2.31</v>
+      </c>
       <c r="AI45" s="1"/>
       <c r="AJ45" s="1"/>
       <c r="AK45" s="1"/>
@@ -10697,7 +10820,7 @@
         <v>35</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-2</v>
       </c>
       <c r="M46" s="1"/>
@@ -10706,7 +10829,7 @@
         <v>54</v>
       </c>
       <c r="P46" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.6</v>
       </c>
       <c r="Q46" s="5"/>
@@ -10722,7 +10845,7 @@
         <v>21.969696969696972</v>
       </c>
       <c r="U46" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>17.424242424242426</v>
       </c>
       <c r="V46" s="1">
@@ -10760,7 +10883,10 @@
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
-      <c r="AH46" s="20"/>
+      <c r="AH46" s="20">
+        <f t="shared" si="8"/>
+        <v>2.64</v>
+      </c>
       <c r="AI46" s="1"/>
       <c r="AJ46" s="1"/>
       <c r="AK46" s="1"/>
@@ -10811,7 +10937,7 @@
         <v>30</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-6</v>
       </c>
       <c r="M47" s="1"/>
@@ -10820,11 +10946,11 @@
         <v>14</v>
       </c>
       <c r="P47" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.8</v>
       </c>
       <c r="Q47" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>28</v>
       </c>
       <c r="R47" s="5">
@@ -10839,7 +10965,7 @@
         <v>21.666666666666668</v>
       </c>
       <c r="U47" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.1666666666666679</v>
       </c>
       <c r="V47" s="1">
@@ -10877,7 +11003,10 @@
         <f t="shared" si="7"/>
         <v>19.8</v>
       </c>
-      <c r="AH47" s="20"/>
+      <c r="AH47" s="20">
+        <f t="shared" si="8"/>
+        <v>1.5840000000000001</v>
+      </c>
       <c r="AI47" s="1"/>
       <c r="AJ47" s="1"/>
       <c r="AK47" s="1"/>
@@ -10928,7 +11057,7 @@
         <v>286</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5.3999999999973625E-2</v>
       </c>
       <c r="M48" s="1"/>
@@ -10937,15 +11066,15 @@
         <v>350</v>
       </c>
       <c r="P48" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>57.210799999999992</v>
       </c>
       <c r="Q48" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>277.66999999999996</v>
       </c>
       <c r="R48" s="5">
-        <f t="shared" ref="R44:R49" si="16">S48</f>
+        <f t="shared" ref="R48" si="17">S48</f>
         <v>400</v>
       </c>
       <c r="S48" s="22">
@@ -10957,7 +11086,7 @@
         <v>17.13823264138939</v>
       </c>
       <c r="U48" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.146545757094815</v>
       </c>
       <c r="V48" s="1">
@@ -10995,7 +11124,10 @@
         <f t="shared" si="7"/>
         <v>400</v>
       </c>
-      <c r="AH48" s="20"/>
+      <c r="AH48" s="20">
+        <f t="shared" si="8"/>
+        <v>57.210799999999992</v>
+      </c>
       <c r="AI48" s="1"/>
       <c r="AJ48" s="1"/>
       <c r="AK48" s="1"/>
@@ -11046,7 +11178,7 @@
         <v>19</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-7</v>
       </c>
       <c r="M49" s="1"/>
@@ -11055,7 +11187,7 @@
         <v>0</v>
       </c>
       <c r="P49" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.4</v>
       </c>
       <c r="Q49" s="5"/>
@@ -11069,7 +11201,7 @@
         <v>23.75</v>
       </c>
       <c r="U49" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>23.75</v>
       </c>
       <c r="V49" s="1">
@@ -11109,7 +11241,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH49" s="20"/>
+      <c r="AH49" s="20">
+        <f t="shared" si="8"/>
+        <v>0.96</v>
+      </c>
       <c r="AI49" s="1"/>
       <c r="AJ49" s="1"/>
       <c r="AK49" s="1"/>
@@ -11156,7 +11291,7 @@
       </c>
       <c r="K50" s="11"/>
       <c r="L50" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M50" s="11"/>
@@ -11165,12 +11300,12 @@
         <v>0</v>
       </c>
       <c r="P50" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q50" s="14"/>
       <c r="R50" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="S50" s="22"/>
@@ -11179,7 +11314,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U50" s="11" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V50" s="11">
@@ -11219,7 +11354,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH50" s="20"/>
+      <c r="AH50" s="20">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AI50" s="1"/>
       <c r="AJ50" s="1"/>
       <c r="AK50" s="1"/>
@@ -11270,7 +11408,7 @@
         <v>54.5</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-0.41199999999999903</v>
       </c>
       <c r="M51" s="1"/>
@@ -11279,11 +11417,11 @@
         <v>30</v>
       </c>
       <c r="P51" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.817600000000001</v>
       </c>
       <c r="Q51" s="5">
-        <f t="shared" ref="Q51:Q67" si="17">15*P51-O51-F51</f>
+        <f t="shared" ref="Q51:Q67" si="18">15*P51-O51-F51</f>
         <v>16.659000000000006</v>
       </c>
       <c r="R51" s="5">
@@ -11298,7 +11436,7 @@
         <v>20.8553653305724</v>
       </c>
       <c r="U51" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13.460009613962432</v>
       </c>
       <c r="V51" s="1">
@@ -11336,7 +11474,10 @@
         <f t="shared" si="7"/>
         <v>80</v>
       </c>
-      <c r="AH51" s="20"/>
+      <c r="AH51" s="20">
+        <f t="shared" si="8"/>
+        <v>10.817600000000001</v>
+      </c>
       <c r="AI51" s="1"/>
       <c r="AJ51" s="1"/>
       <c r="AK51" s="1"/>
@@ -11383,7 +11524,7 @@
         <v>5.9</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-5.9</v>
       </c>
       <c r="M52" s="1"/>
@@ -11392,14 +11533,14 @@
         <v>12</v>
       </c>
       <c r="P52" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q52" s="5">
         <v>4</v>
       </c>
       <c r="R52" s="5">
-        <f t="shared" ref="R51:R53" si="18">S52</f>
+        <f t="shared" ref="R52:R53" si="19">S52</f>
         <v>50</v>
       </c>
       <c r="S52" s="22">
@@ -11411,7 +11552,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U52" s="1" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V52" s="1">
@@ -11451,7 +11592,10 @@
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="AH52" s="20"/>
+      <c r="AH52" s="20">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AI52" s="1"/>
       <c r="AJ52" s="1"/>
       <c r="AK52" s="1"/>
@@ -11500,7 +11644,7 @@
         <v>40</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M53" s="1"/>
@@ -11509,7 +11653,7 @@
         <v>0</v>
       </c>
       <c r="P53" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8</v>
       </c>
       <c r="Q53" s="5">
@@ -11517,7 +11661,7 @@
         <v>74</v>
       </c>
       <c r="R53" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>150</v>
       </c>
       <c r="S53" s="22">
@@ -11529,7 +11673,7 @@
         <v>22.5</v>
       </c>
       <c r="U53" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3.75</v>
       </c>
       <c r="V53" s="1">
@@ -11567,7 +11711,10 @@
         <f t="shared" si="7"/>
         <v>37.5</v>
       </c>
-      <c r="AH53" s="20"/>
+      <c r="AH53" s="20">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
       <c r="AI53" s="1"/>
       <c r="AJ53" s="1"/>
       <c r="AK53" s="1"/>
@@ -11618,7 +11765,7 @@
         <v>30</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-7.5139999999999993</v>
       </c>
       <c r="M54" s="1"/>
@@ -11627,12 +11774,12 @@
         <v>190</v>
       </c>
       <c r="P54" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.4972000000000003</v>
       </c>
       <c r="Q54" s="5"/>
       <c r="R54" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="S54" s="22"/>
@@ -11641,7 +11788,7 @@
         <v>53.660944587743487</v>
       </c>
       <c r="U54" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>53.660944587743487</v>
       </c>
       <c r="V54" s="1">
@@ -11679,7 +11826,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH54" s="20"/>
+      <c r="AH54" s="20">
+        <f t="shared" si="8"/>
+        <v>4.4972000000000003</v>
+      </c>
       <c r="AI54" s="1"/>
       <c r="AJ54" s="1"/>
       <c r="AK54" s="1"/>
@@ -11728,7 +11878,7 @@
         <v>85</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-9</v>
       </c>
       <c r="M55" s="1"/>
@@ -11737,11 +11887,11 @@
         <v>100</v>
       </c>
       <c r="P55" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>15.2</v>
       </c>
       <c r="Q55" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>8</v>
       </c>
       <c r="R55" s="5">
@@ -11756,7 +11906,7 @@
         <v>19.736842105263158</v>
       </c>
       <c r="U55" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>14.473684210526317</v>
       </c>
       <c r="V55" s="1">
@@ -11796,7 +11946,10 @@
         <f t="shared" si="7"/>
         <v>21.6</v>
       </c>
-      <c r="AH55" s="20"/>
+      <c r="AH55" s="20">
+        <f t="shared" si="8"/>
+        <v>4.1040000000000001</v>
+      </c>
       <c r="AI55" s="1"/>
       <c r="AJ55" s="1"/>
       <c r="AK55" s="1"/>
@@ -11845,7 +11998,7 @@
         <v>20</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M56" s="1"/>
@@ -11854,7 +12007,7 @@
         <v>80</v>
       </c>
       <c r="P56" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
       <c r="Q56" s="5"/>
@@ -11870,7 +12023,7 @@
         <v>34.75</v>
       </c>
       <c r="U56" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>29.75</v>
       </c>
       <c r="V56" s="1">
@@ -11910,7 +12063,10 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="AH56" s="20"/>
+      <c r="AH56" s="20">
+        <f t="shared" si="8"/>
+        <v>1.2</v>
+      </c>
       <c r="AI56" s="1"/>
       <c r="AJ56" s="1"/>
       <c r="AK56" s="1"/>
@@ -11962,7 +12118,7 @@
         <v>258</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-45</v>
       </c>
       <c r="M57" s="1"/>
@@ -11971,7 +12127,7 @@
         <v>670</v>
       </c>
       <c r="P57" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>42.6</v>
       </c>
       <c r="Q57" s="5"/>
@@ -11987,7 +12143,7 @@
         <v>21.877934272300468</v>
       </c>
       <c r="U57" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>17.183098591549296</v>
       </c>
       <c r="V57" s="1">
@@ -12026,8 +12182,8 @@
         <v>82</v>
       </c>
       <c r="AH57" s="20">
-        <f>V57/W57</f>
-        <v>1.6214689265536724</v>
+        <f t="shared" si="8"/>
+        <v>17.466000000000001</v>
       </c>
       <c r="AI57" s="1"/>
       <c r="AJ57" s="1"/>
@@ -12079,7 +12235,7 @@
         <v>97.8</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-4.9179999999999922</v>
       </c>
       <c r="M58" s="1"/>
@@ -12088,11 +12244,11 @@
         <v>11</v>
       </c>
       <c r="P58" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>18.5764</v>
       </c>
       <c r="Q58" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>128.52600000000001</v>
       </c>
       <c r="R58" s="5">
@@ -12107,7 +12263,7 @@
         <v>19.924204905148468</v>
       </c>
       <c r="U58" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.0812213345965862</v>
       </c>
       <c r="V58" s="1">
@@ -12145,7 +12301,10 @@
         <f t="shared" si="7"/>
         <v>220</v>
       </c>
-      <c r="AH58" s="20"/>
+      <c r="AH58" s="20">
+        <f t="shared" si="8"/>
+        <v>18.5764</v>
+      </c>
       <c r="AI58" s="1"/>
       <c r="AJ58" s="1"/>
       <c r="AK58" s="1"/>
@@ -12196,7 +12355,7 @@
         <v>22</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-3</v>
       </c>
       <c r="M59" s="1"/>
@@ -12205,7 +12364,7 @@
         <v>0</v>
       </c>
       <c r="P59" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.8</v>
       </c>
       <c r="Q59" s="5"/>
@@ -12221,7 +12380,7 @@
         <v>21.05263157894737</v>
       </c>
       <c r="U59" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15.789473684210527</v>
       </c>
       <c r="V59" s="1">
@@ -12261,7 +12420,10 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="AH59" s="20"/>
+      <c r="AH59" s="20">
+        <f t="shared" si="8"/>
+        <v>1.3299999999999998</v>
+      </c>
       <c r="AI59" s="1"/>
       <c r="AJ59" s="1"/>
       <c r="AK59" s="1"/>
@@ -12312,7 +12474,7 @@
         <v>40.5</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.0399999999999991</v>
       </c>
       <c r="M60" s="1"/>
@@ -12321,11 +12483,11 @@
         <v>0</v>
       </c>
       <c r="P60" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.3079999999999998</v>
       </c>
       <c r="Q60" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>78.343000000000004</v>
       </c>
       <c r="R60" s="5">
@@ -12340,7 +12502,7 @@
         <v>20.014082811747713</v>
       </c>
       <c r="U60" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.5701733269138183</v>
       </c>
       <c r="V60" s="1">
@@ -12378,7 +12540,10 @@
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="AH60" s="20"/>
+      <c r="AH60" s="20">
+        <f t="shared" si="8"/>
+        <v>8.3079999999999998</v>
+      </c>
       <c r="AI60" s="1"/>
       <c r="AJ60" s="1"/>
       <c r="AK60" s="1"/>
@@ -12429,7 +12594,7 @@
         <v>214</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-57</v>
       </c>
       <c r="M61" s="1"/>
@@ -12438,12 +12603,12 @@
         <v>350</v>
       </c>
       <c r="P61" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>31.4</v>
       </c>
       <c r="Q61" s="5"/>
       <c r="R61" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="S61" s="22"/>
@@ -12452,7 +12617,7 @@
         <v>16.751592356687897</v>
       </c>
       <c r="U61" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>16.751592356687897</v>
       </c>
       <c r="V61" s="1">
@@ -12490,7 +12655,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH61" s="20"/>
+      <c r="AH61" s="20">
+        <f t="shared" si="8"/>
+        <v>12.873999999999999</v>
+      </c>
       <c r="AI61" s="1"/>
       <c r="AJ61" s="1"/>
       <c r="AK61" s="1"/>
@@ -12541,7 +12709,7 @@
         <v>119</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.1159999999999997</v>
       </c>
       <c r="M62" s="1"/>
@@ -12550,11 +12718,11 @@
         <v>26</v>
       </c>
       <c r="P62" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>24.623200000000001</v>
       </c>
       <c r="Q62" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>220.57300000000001</v>
       </c>
       <c r="R62" s="5">
@@ -12569,7 +12737,7 @@
         <v>20.256302998797882</v>
       </c>
       <c r="U62" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.0420660190389555</v>
       </c>
       <c r="V62" s="1">
@@ -12607,7 +12775,10 @@
         <f t="shared" si="7"/>
         <v>350</v>
       </c>
-      <c r="AH62" s="20"/>
+      <c r="AH62" s="20">
+        <f t="shared" si="8"/>
+        <v>24.623200000000001</v>
+      </c>
       <c r="AI62" s="1"/>
       <c r="AJ62" s="1"/>
       <c r="AK62" s="1"/>
@@ -12658,7 +12829,7 @@
         <v>74</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-12</v>
       </c>
       <c r="M63" s="1"/>
@@ -12667,11 +12838,11 @@
         <v>25</v>
       </c>
       <c r="P63" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>12.4</v>
       </c>
       <c r="Q63" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>60</v>
       </c>
       <c r="R63" s="5">
@@ -12686,7 +12857,7 @@
         <v>19.838709677419356</v>
       </c>
       <c r="U63" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.161290322580644</v>
       </c>
       <c r="V63" s="1">
@@ -12724,7 +12895,10 @@
         <f t="shared" si="7"/>
         <v>36</v>
       </c>
-      <c r="AH63" s="20"/>
+      <c r="AH63" s="20">
+        <f t="shared" si="8"/>
+        <v>3.7199999999999998</v>
+      </c>
       <c r="AI63" s="1"/>
       <c r="AJ63" s="1"/>
       <c r="AK63" s="1"/>
@@ -12769,7 +12943,7 @@
         <v>75</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-76</v>
       </c>
       <c r="M64" s="1"/>
@@ -12778,7 +12952,7 @@
         <v>60</v>
       </c>
       <c r="P64" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-0.2</v>
       </c>
       <c r="Q64" s="5">
@@ -12796,7 +12970,7 @@
         <v>-800</v>
       </c>
       <c r="U64" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-300</v>
       </c>
       <c r="V64" s="1">
@@ -12836,7 +13010,10 @@
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
-      <c r="AH64" s="20"/>
+      <c r="AH64" s="20">
+        <f t="shared" si="8"/>
+        <v>-3.5999999999999997E-2</v>
+      </c>
       <c r="AI64" s="1"/>
       <c r="AJ64" s="1"/>
       <c r="AK64" s="1"/>
@@ -12887,7 +13064,7 @@
         <v>26</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-3</v>
       </c>
       <c r="M65" s="1"/>
@@ -12896,15 +13073,15 @@
         <v>20</v>
       </c>
       <c r="P65" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="Q65" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>27</v>
       </c>
       <c r="R65" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>27</v>
       </c>
       <c r="S65" s="22"/>
@@ -12913,7 +13090,7 @@
         <v>15.000000000000002</v>
       </c>
       <c r="U65" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.1304347826086971</v>
       </c>
       <c r="V65" s="1">
@@ -12953,7 +13130,10 @@
         <f t="shared" si="7"/>
         <v>5.94</v>
       </c>
-      <c r="AH65" s="20"/>
+      <c r="AH65" s="20">
+        <f t="shared" si="8"/>
+        <v>1.012</v>
+      </c>
       <c r="AI65" s="1"/>
       <c r="AJ65" s="1"/>
       <c r="AK65" s="1"/>
@@ -13002,7 +13182,7 @@
         <v>25</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1</v>
       </c>
       <c r="M66" s="1"/>
@@ -13011,15 +13191,15 @@
         <v>0</v>
       </c>
       <c r="P66" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.8</v>
       </c>
       <c r="Q66" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>22</v>
       </c>
       <c r="R66" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>22</v>
       </c>
       <c r="S66" s="22"/>
@@ -13028,7 +13208,7 @@
         <v>15</v>
       </c>
       <c r="U66" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.416666666666668</v>
       </c>
       <c r="V66" s="1">
@@ -13066,7 +13246,10 @@
         <f t="shared" si="7"/>
         <v>18.48</v>
       </c>
-      <c r="AH66" s="20"/>
+      <c r="AH66" s="20">
+        <f t="shared" si="8"/>
+        <v>4.032</v>
+      </c>
       <c r="AI66" s="1"/>
       <c r="AJ66" s="1"/>
       <c r="AK66" s="1"/>
@@ -13117,7 +13300,7 @@
         <v>470.4</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-45.399999999999977</v>
       </c>
       <c r="M67" s="1"/>
@@ -13126,11 +13309,11 @@
         <v>500</v>
       </c>
       <c r="P67" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>85</v>
       </c>
       <c r="Q67" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>559</v>
       </c>
       <c r="R67" s="5">
@@ -13146,7 +13329,7 @@
         <v>16.658823529411766</v>
       </c>
       <c r="U67" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.4235294117647062</v>
       </c>
       <c r="V67" s="1">
@@ -13184,7 +13367,10 @@
         <f t="shared" si="7"/>
         <v>244.99999999999997</v>
       </c>
-      <c r="AH67" s="20"/>
+      <c r="AH67" s="20">
+        <f t="shared" si="8"/>
+        <v>29.749999999999996</v>
+      </c>
       <c r="AI67" s="1"/>
       <c r="AJ67" s="1"/>
       <c r="AK67" s="1"/>
@@ -13223,7 +13409,7 @@
       <c r="J68" s="11"/>
       <c r="K68" s="11"/>
       <c r="L68" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M68" s="11"/>
@@ -13232,12 +13418,12 @@
         <v>0</v>
       </c>
       <c r="P68" s="11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q68" s="14"/>
       <c r="R68" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="S68" s="22"/>
@@ -13246,7 +13432,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U68" s="11" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V68" s="11">
@@ -13286,7 +13472,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH68" s="20"/>
+      <c r="AH68" s="20">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AI68" s="1"/>
       <c r="AJ68" s="1"/>
       <c r="AK68" s="1"/>
@@ -13337,7 +13526,7 @@
         <v>191.8</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-40.03</v>
       </c>
       <c r="M69" s="1"/>
@@ -13346,15 +13535,15 @@
         <v>180</v>
       </c>
       <c r="P69" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>30.354000000000003</v>
       </c>
       <c r="Q69" s="5">
-        <f t="shared" ref="Q69:Q77" si="19">15*P69-O69-F69</f>
+        <f t="shared" ref="Q69:Q77" si="20">15*P69-O69-F69</f>
         <v>37.08400000000006</v>
       </c>
       <c r="R69" s="5">
-        <f t="shared" ref="R69:R72" si="20">S69</f>
+        <f t="shared" ref="R69:R71" si="21">S69</f>
         <v>100</v>
       </c>
       <c r="S69" s="22">
@@ -13366,7 +13555,7 @@
         <v>17.072741648547144</v>
       </c>
       <c r="U69" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13.77828292811491</v>
       </c>
       <c r="V69" s="1">
@@ -13404,7 +13593,10 @@
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="AH69" s="20"/>
+      <c r="AH69" s="20">
+        <f t="shared" si="8"/>
+        <v>30.354000000000003</v>
+      </c>
       <c r="AI69" s="1"/>
       <c r="AJ69" s="1"/>
       <c r="AK69" s="1"/>
@@ -13455,7 +13647,7 @@
         <v>216.8</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="21">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="22">E70-K70</f>
         <v>-35.722000000000008</v>
       </c>
       <c r="M70" s="1"/>
@@ -13464,15 +13656,15 @@
         <v>170</v>
       </c>
       <c r="P70" s="1">
-        <f t="shared" ref="P70:P101" si="22">E70/5</f>
+        <f t="shared" ref="P70:P101" si="23">E70/5</f>
         <v>36.215600000000002</v>
       </c>
       <c r="Q70" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>85.735000000000014</v>
       </c>
       <c r="R70" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>160</v>
       </c>
       <c r="S70" s="22">
@@ -13484,7 +13676,7 @@
         <v>17.050635637680998</v>
       </c>
       <c r="U70" s="1">
-        <f t="shared" ref="U70:U101" si="23">(F70+O70)/P70</f>
+        <f t="shared" ref="U70:U101" si="24">(F70+O70)/P70</f>
         <v>12.63265001822419</v>
       </c>
       <c r="V70" s="1">
@@ -13522,7 +13714,10 @@
         <f t="shared" si="7"/>
         <v>160</v>
       </c>
-      <c r="AH70" s="20"/>
+      <c r="AH70" s="20">
+        <f t="shared" si="8"/>
+        <v>36.215600000000002</v>
+      </c>
       <c r="AI70" s="1"/>
       <c r="AJ70" s="1"/>
       <c r="AK70" s="1"/>
@@ -13573,7 +13768,7 @@
         <v>490</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-53</v>
       </c>
       <c r="M71" s="1"/>
@@ -13582,15 +13777,15 @@
         <v>450</v>
       </c>
       <c r="P71" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>87.4</v>
       </c>
       <c r="Q71" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>682</v>
       </c>
       <c r="R71" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>800</v>
       </c>
       <c r="S71" s="22">
@@ -13598,11 +13793,11 @@
         <v>800</v>
       </c>
       <c r="T71" s="1">
-        <f t="shared" ref="T71:T107" si="24">(F71+O71+R71)/P71</f>
+        <f t="shared" ref="T71:T107" si="25">(F71+O71+R71)/P71</f>
         <v>16.350114416475972</v>
       </c>
       <c r="U71" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>7.196796338672768</v>
       </c>
       <c r="V71" s="1">
@@ -13637,10 +13832,13 @@
       </c>
       <c r="AF71" s="1"/>
       <c r="AG71" s="1">
-        <f t="shared" ref="AG71:AG107" si="25">G71*R71</f>
+        <f t="shared" ref="AG71:AG107" si="26">G71*R71</f>
         <v>280</v>
       </c>
-      <c r="AH71" s="20"/>
+      <c r="AH71" s="20">
+        <f t="shared" ref="AH71:AH107" si="27">P71*G71</f>
+        <v>30.59</v>
+      </c>
       <c r="AI71" s="1"/>
       <c r="AJ71" s="1"/>
       <c r="AK71" s="1"/>
@@ -13691,7 +13889,7 @@
         <v>104</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-7</v>
       </c>
       <c r="M72" s="1"/>
@@ -13700,11 +13898,11 @@
         <v>100</v>
       </c>
       <c r="P72" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>19.399999999999999</v>
       </c>
       <c r="Q72" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>132</v>
       </c>
       <c r="R72" s="5">
@@ -13715,11 +13913,11 @@
         <v>240</v>
       </c>
       <c r="T72" s="1">
+        <f t="shared" si="25"/>
+        <v>19.536082474226806</v>
+      </c>
+      <c r="U72" s="1">
         <f t="shared" si="24"/>
-        <v>19.536082474226806</v>
-      </c>
-      <c r="U72" s="1">
-        <f t="shared" si="23"/>
         <v>8.1958762886597949</v>
       </c>
       <c r="V72" s="1">
@@ -13754,10 +13952,13 @@
       </c>
       <c r="AF72" s="1"/>
       <c r="AG72" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>66</v>
       </c>
-      <c r="AH72" s="20"/>
+      <c r="AH72" s="20">
+        <f t="shared" si="27"/>
+        <v>5.8199999999999994</v>
+      </c>
       <c r="AI72" s="1"/>
       <c r="AJ72" s="1"/>
       <c r="AK72" s="1"/>
@@ -13806,7 +14007,7 @@
         <v>59</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-4</v>
       </c>
       <c r="M73" s="1"/>
@@ -13815,24 +14016,24 @@
         <v>120</v>
       </c>
       <c r="P73" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="Q73" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>45</v>
       </c>
       <c r="R73" s="5">
-        <f t="shared" ref="R71:R107" si="26">ROUND(Q73,0)</f>
+        <f t="shared" ref="R73:R107" si="28">ROUND(Q73,0)</f>
         <v>45</v>
       </c>
       <c r="S73" s="22"/>
       <c r="T73" s="1">
+        <f t="shared" si="25"/>
+        <v>15</v>
+      </c>
+      <c r="U73" s="1">
         <f t="shared" si="24"/>
-        <v>15</v>
-      </c>
-      <c r="U73" s="1">
-        <f t="shared" si="23"/>
         <v>10.909090909090908</v>
       </c>
       <c r="V73" s="1">
@@ -13867,10 +14068,13 @@
       </c>
       <c r="AF73" s="1"/>
       <c r="AG73" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>13.5</v>
       </c>
-      <c r="AH73" s="20"/>
+      <c r="AH73" s="20">
+        <f t="shared" si="27"/>
+        <v>3.3</v>
+      </c>
       <c r="AI73" s="1"/>
       <c r="AJ73" s="1"/>
       <c r="AK73" s="1"/>
@@ -13921,7 +14125,7 @@
         <v>294</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-67</v>
       </c>
       <c r="M74" s="1"/>
@@ -13930,24 +14134,24 @@
         <v>630</v>
       </c>
       <c r="P74" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>45.4</v>
       </c>
       <c r="Q74" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>42</v>
       </c>
       <c r="R74" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>42</v>
       </c>
       <c r="S74" s="22"/>
       <c r="T74" s="1">
+        <f t="shared" si="25"/>
+        <v>15</v>
+      </c>
+      <c r="U74" s="1">
         <f t="shared" si="24"/>
-        <v>15</v>
-      </c>
-      <c r="U74" s="1">
-        <f t="shared" si="23"/>
         <v>14.07488986784141</v>
       </c>
       <c r="V74" s="1">
@@ -13982,10 +14186,13 @@
       </c>
       <c r="AF74" s="1"/>
       <c r="AG74" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>11.760000000000002</v>
       </c>
-      <c r="AH74" s="20"/>
+      <c r="AH74" s="20">
+        <f t="shared" si="27"/>
+        <v>12.712000000000002</v>
+      </c>
       <c r="AI74" s="1"/>
       <c r="AJ74" s="1"/>
       <c r="AK74" s="1"/>
@@ -14036,7 +14243,7 @@
         <v>354</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-69</v>
       </c>
       <c r="M75" s="1"/>
@@ -14045,15 +14252,15 @@
         <v>650</v>
       </c>
       <c r="P75" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>57</v>
       </c>
       <c r="Q75" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>161</v>
       </c>
       <c r="R75" s="5">
-        <f t="shared" ref="R75:R77" si="27">S75</f>
+        <f t="shared" ref="R75:R77" si="29">S75</f>
         <v>300</v>
       </c>
       <c r="S75" s="22">
@@ -14061,11 +14268,11 @@
         <v>300</v>
       </c>
       <c r="T75" s="1">
+        <f t="shared" si="25"/>
+        <v>17.438596491228068</v>
+      </c>
+      <c r="U75" s="1">
         <f t="shared" si="24"/>
-        <v>17.438596491228068</v>
-      </c>
-      <c r="U75" s="1">
-        <f t="shared" si="23"/>
         <v>12.175438596491228</v>
       </c>
       <c r="V75" s="1">
@@ -14100,10 +14307,13 @@
       </c>
       <c r="AF75" s="1"/>
       <c r="AG75" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>84.000000000000014</v>
       </c>
-      <c r="AH75" s="20"/>
+      <c r="AH75" s="20">
+        <f t="shared" si="27"/>
+        <v>15.96</v>
+      </c>
       <c r="AI75" s="1"/>
       <c r="AJ75" s="1"/>
       <c r="AK75" s="1"/>
@@ -14154,7 +14364,7 @@
         <v>218</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-35</v>
       </c>
       <c r="M76" s="1"/>
@@ -14163,15 +14373,15 @@
         <v>380</v>
       </c>
       <c r="P76" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>36.6</v>
       </c>
       <c r="Q76" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>152</v>
       </c>
       <c r="R76" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="S76" s="22">
@@ -14179,11 +14389,11 @@
         <v>300</v>
       </c>
       <c r="T76" s="1">
+        <f t="shared" si="25"/>
+        <v>19.043715846994534</v>
+      </c>
+      <c r="U76" s="1">
         <f t="shared" si="24"/>
-        <v>19.043715846994534</v>
-      </c>
-      <c r="U76" s="1">
-        <f t="shared" si="23"/>
         <v>10.846994535519125</v>
       </c>
       <c r="V76" s="1">
@@ -14218,10 +14428,13 @@
       </c>
       <c r="AF76" s="1"/>
       <c r="AG76" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>84.000000000000014</v>
       </c>
-      <c r="AH76" s="20"/>
+      <c r="AH76" s="20">
+        <f t="shared" si="27"/>
+        <v>10.248000000000001</v>
+      </c>
       <c r="AI76" s="1"/>
       <c r="AJ76" s="1"/>
       <c r="AK76" s="1"/>
@@ -14272,7 +14485,7 @@
         <v>210</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-23</v>
       </c>
       <c r="M77" s="1"/>
@@ -14281,15 +14494,15 @@
         <v>510</v>
       </c>
       <c r="P77" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>37.4</v>
       </c>
       <c r="Q77" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>42</v>
       </c>
       <c r="R77" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>200</v>
       </c>
       <c r="S77" s="22">
@@ -14297,11 +14510,11 @@
         <v>200</v>
       </c>
       <c r="T77" s="1">
+        <f t="shared" si="25"/>
+        <v>19.224598930481285</v>
+      </c>
+      <c r="U77" s="1">
         <f t="shared" si="24"/>
-        <v>19.224598930481285</v>
-      </c>
-      <c r="U77" s="1">
-        <f t="shared" si="23"/>
         <v>13.877005347593583</v>
       </c>
       <c r="V77" s="1">
@@ -14336,10 +14549,13 @@
       </c>
       <c r="AF77" s="1"/>
       <c r="AG77" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>80</v>
       </c>
-      <c r="AH77" s="20"/>
+      <c r="AH77" s="20">
+        <f t="shared" si="27"/>
+        <v>14.96</v>
+      </c>
       <c r="AI77" s="1"/>
       <c r="AJ77" s="1"/>
       <c r="AK77" s="1"/>
@@ -14386,7 +14602,7 @@
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M78" s="1"/>
@@ -14395,61 +14611,64 @@
         <v>0</v>
       </c>
       <c r="P78" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="Q78" s="5"/>
       <c r="R78" s="5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="S78" s="22"/>
+      <c r="T78" s="1" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U78" s="1" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V78" s="1">
+        <v>0</v>
+      </c>
+      <c r="W78" s="1">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="X78" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="1">
+        <v>-6.1199999999999997E-2</v>
+      </c>
+      <c r="AA78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="1">
+        <v>-0.16059999999999999</v>
+      </c>
+      <c r="AD78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="AG78" s="1">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="S78" s="22"/>
-      <c r="T78" s="1" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U78" s="1" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V78" s="1">
+      <c r="AH78" s="20">
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="W78" s="1">
-        <v>0.13700000000000001</v>
-      </c>
-      <c r="X78" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y78" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z78" s="1">
-        <v>-6.1199999999999997E-2</v>
-      </c>
-      <c r="AA78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC78" s="1">
-        <v>-0.16059999999999999</v>
-      </c>
-      <c r="AD78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE78" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF78" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="AG78" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AH78" s="20"/>
       <c r="AI78" s="1"/>
       <c r="AJ78" s="1"/>
       <c r="AK78" s="1"/>
@@ -14498,7 +14717,7 @@
         <v>20</v>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2</v>
       </c>
       <c r="M79" s="1"/>
@@ -14507,61 +14726,64 @@
         <v>0</v>
       </c>
       <c r="P79" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="Q79" s="5"/>
       <c r="R79" s="5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="S79" s="22"/>
+      <c r="T79" s="1">
+        <f t="shared" si="25"/>
+        <v>35.227272727272727</v>
+      </c>
+      <c r="U79" s="1">
+        <f t="shared" si="24"/>
+        <v>35.227272727272727</v>
+      </c>
+      <c r="V79" s="1">
+        <v>6</v>
+      </c>
+      <c r="W79" s="1">
+        <v>0</v>
+      </c>
+      <c r="X79" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Y79" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="Z79" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="AA79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF79" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG79" s="1">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="S79" s="22"/>
-      <c r="T79" s="1">
-        <f t="shared" si="24"/>
-        <v>35.227272727272727</v>
-      </c>
-      <c r="U79" s="1">
-        <f t="shared" si="23"/>
-        <v>35.227272727272727</v>
-      </c>
-      <c r="V79" s="1">
-        <v>6</v>
-      </c>
-      <c r="W79" s="1">
-        <v>0</v>
-      </c>
-      <c r="X79" s="1">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="Y79" s="1">
-        <v>8.6</v>
-      </c>
-      <c r="Z79" s="1">
-        <v>5.2</v>
-      </c>
-      <c r="AA79" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB79" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC79" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD79" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE79" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF79" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="AG79" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AH79" s="20"/>
+      <c r="AH79" s="20">
+        <f t="shared" si="27"/>
+        <v>1.4872000000000003</v>
+      </c>
       <c r="AI79" s="1"/>
       <c r="AJ79" s="1"/>
       <c r="AK79" s="1"/>
@@ -14610,7 +14832,7 @@
         <v>20</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M80" s="1"/>
@@ -14619,61 +14841,64 @@
         <v>0</v>
       </c>
       <c r="P80" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>4</v>
       </c>
       <c r="Q80" s="5"/>
       <c r="R80" s="5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="S80" s="22"/>
+      <c r="T80" s="1">
+        <f t="shared" si="25"/>
+        <v>31.25</v>
+      </c>
+      <c r="U80" s="1">
+        <f t="shared" si="24"/>
+        <v>31.25</v>
+      </c>
+      <c r="V80" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="W80" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="X80" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Y80" s="1">
+        <v>11.6</v>
+      </c>
+      <c r="Z80" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="AA80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG80" s="1">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="S80" s="22"/>
-      <c r="T80" s="1">
-        <f t="shared" si="24"/>
-        <v>31.25</v>
-      </c>
-      <c r="U80" s="1">
-        <f t="shared" si="23"/>
-        <v>31.25</v>
-      </c>
-      <c r="V80" s="1">
-        <v>5.6</v>
-      </c>
-      <c r="W80" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="X80" s="1">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="Y80" s="1">
-        <v>11.6</v>
-      </c>
-      <c r="Z80" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="AA80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF80" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="AG80" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AH80" s="20"/>
+      <c r="AH80" s="20">
+        <f t="shared" si="27"/>
+        <v>1.3</v>
+      </c>
       <c r="AI80" s="1"/>
       <c r="AJ80" s="1"/>
       <c r="AK80" s="1"/>
@@ -14724,7 +14949,7 @@
         <v>265</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-34</v>
       </c>
       <c r="M81" s="1"/>
@@ -14733,7 +14958,7 @@
         <v>207</v>
       </c>
       <c r="P81" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>46.2</v>
       </c>
       <c r="Q81" s="5">
@@ -14749,11 +14974,11 @@
         <v>600</v>
       </c>
       <c r="T81" s="1">
+        <f t="shared" si="25"/>
+        <v>17.121212121212121</v>
+      </c>
+      <c r="U81" s="1">
         <f t="shared" si="24"/>
-        <v>17.121212121212121</v>
-      </c>
-      <c r="U81" s="1">
-        <f t="shared" si="23"/>
         <v>4.1341991341991342</v>
       </c>
       <c r="V81" s="1">
@@ -14788,10 +15013,13 @@
       </c>
       <c r="AF81" s="1"/>
       <c r="AG81" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>72</v>
       </c>
-      <c r="AH81" s="20"/>
+      <c r="AH81" s="20">
+        <f t="shared" si="27"/>
+        <v>5.5440000000000005</v>
+      </c>
       <c r="AI81" s="1"/>
       <c r="AJ81" s="1"/>
       <c r="AK81" s="1"/>
@@ -14842,7 +15070,7 @@
         <v>61</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-4</v>
       </c>
       <c r="M82" s="1"/>
@@ -14851,61 +15079,64 @@
         <v>0</v>
       </c>
       <c r="P82" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11.4</v>
       </c>
       <c r="Q82" s="5"/>
       <c r="R82" s="5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="S82" s="22"/>
+      <c r="T82" s="1">
+        <f t="shared" si="25"/>
+        <v>22.280701754385966</v>
+      </c>
+      <c r="U82" s="1">
+        <f t="shared" si="24"/>
+        <v>22.280701754385966</v>
+      </c>
+      <c r="V82" s="1">
+        <v>15</v>
+      </c>
+      <c r="W82" s="1">
+        <v>11.6</v>
+      </c>
+      <c r="X82" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="Y82" s="1">
+        <v>16.8</v>
+      </c>
+      <c r="Z82" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="AA82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF82" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG82" s="1">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="S82" s="22"/>
-      <c r="T82" s="1">
-        <f t="shared" si="24"/>
-        <v>22.280701754385966</v>
-      </c>
-      <c r="U82" s="1">
-        <f t="shared" si="23"/>
-        <v>22.280701754385966</v>
-      </c>
-      <c r="V82" s="1">
-        <v>15</v>
-      </c>
-      <c r="W82" s="1">
-        <v>11.6</v>
-      </c>
-      <c r="X82" s="1">
-        <v>3.6</v>
-      </c>
-      <c r="Y82" s="1">
-        <v>16.8</v>
-      </c>
-      <c r="Z82" s="1">
-        <v>2.8</v>
-      </c>
-      <c r="AA82" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB82" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC82" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD82" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE82" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF82" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="AG82" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AH82" s="20"/>
+      <c r="AH82" s="20">
+        <f t="shared" si="27"/>
+        <v>1.71</v>
+      </c>
       <c r="AI82" s="1"/>
       <c r="AJ82" s="1"/>
       <c r="AK82" s="1"/>
@@ -14956,7 +15187,7 @@
         <v>54</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-5</v>
       </c>
       <c r="M83" s="1"/>
@@ -14965,61 +15196,64 @@
         <v>0</v>
       </c>
       <c r="P83" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>9.8000000000000007</v>
       </c>
       <c r="Q83" s="5"/>
       <c r="R83" s="5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="S83" s="22"/>
+      <c r="T83" s="1">
+        <f t="shared" si="25"/>
+        <v>27.142857142857142</v>
+      </c>
+      <c r="U83" s="1">
+        <f t="shared" si="24"/>
+        <v>27.142857142857142</v>
+      </c>
+      <c r="V83" s="1">
+        <v>15.2</v>
+      </c>
+      <c r="W83" s="1">
+        <v>13</v>
+      </c>
+      <c r="X83" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Y83" s="1">
+        <v>14.2</v>
+      </c>
+      <c r="Z83" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="AA83" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG83" s="1">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="S83" s="22"/>
-      <c r="T83" s="1">
-        <f t="shared" si="24"/>
-        <v>27.142857142857142</v>
-      </c>
-      <c r="U83" s="1">
-        <f t="shared" si="23"/>
-        <v>27.142857142857142</v>
-      </c>
-      <c r="V83" s="1">
-        <v>15.2</v>
-      </c>
-      <c r="W83" s="1">
-        <v>13</v>
-      </c>
-      <c r="X83" s="1">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="Y83" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="Z83" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="AA83" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB83" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC83" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD83" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE83" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF83" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="AG83" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AH83" s="20"/>
+      <c r="AH83" s="20">
+        <f t="shared" si="27"/>
+        <v>1.47</v>
+      </c>
       <c r="AI83" s="1"/>
       <c r="AJ83" s="1"/>
       <c r="AK83" s="1"/>
@@ -15070,7 +15304,7 @@
         <v>86</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="M84" s="1"/>
@@ -15079,7 +15313,7 @@
         <v>16</v>
       </c>
       <c r="P84" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>18.2</v>
       </c>
       <c r="Q84" s="5">
@@ -15087,7 +15321,7 @@
         <v>142.79999999999998</v>
       </c>
       <c r="R84" s="5">
-        <f t="shared" ref="R84:R87" si="28">S84</f>
+        <f t="shared" ref="R84:R86" si="30">S84</f>
         <v>200</v>
       </c>
       <c r="S84" s="22">
@@ -15095,11 +15329,11 @@
         <v>200</v>
       </c>
       <c r="T84" s="1">
+        <f t="shared" si="25"/>
+        <v>12.142857142857144</v>
+      </c>
+      <c r="U84" s="1">
         <f t="shared" si="24"/>
-        <v>12.142857142857144</v>
-      </c>
-      <c r="U84" s="1">
-        <f t="shared" si="23"/>
         <v>1.153846153846154</v>
       </c>
       <c r="V84" s="1">
@@ -15136,10 +15370,13 @@
         <v>138</v>
       </c>
       <c r="AG84" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>66</v>
       </c>
-      <c r="AH84" s="20"/>
+      <c r="AH84" s="20">
+        <f t="shared" si="27"/>
+        <v>6.0060000000000002</v>
+      </c>
       <c r="AI84" s="1"/>
       <c r="AJ84" s="1"/>
       <c r="AK84" s="1"/>
@@ -15190,7 +15427,7 @@
         <v>57</v>
       </c>
       <c r="L85" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-10</v>
       </c>
       <c r="M85" s="1"/>
@@ -15199,7 +15436,7 @@
         <v>0</v>
       </c>
       <c r="P85" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>9.4</v>
       </c>
       <c r="Q85" s="5"/>
@@ -15209,13 +15446,13 @@
         <v>100</v>
       </c>
       <c r="T85" s="1">
+        <f t="shared" si="25"/>
+        <v>24.574468085106382</v>
+      </c>
+      <c r="U85" s="1">
         <f t="shared" si="24"/>
         <v>24.574468085106382</v>
       </c>
-      <c r="U85" s="1">
-        <f t="shared" si="23"/>
-        <v>24.574468085106382</v>
-      </c>
       <c r="V85" s="1">
         <v>6.2</v>
       </c>
@@ -15250,10 +15487,13 @@
         <v>168</v>
       </c>
       <c r="AG85" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AH85" s="20"/>
+      <c r="AH85" s="20">
+        <f t="shared" si="27"/>
+        <v>1.41</v>
+      </c>
       <c r="AI85" s="1"/>
       <c r="AJ85" s="1"/>
       <c r="AK85" s="1"/>
@@ -15305,7 +15545,7 @@
         <v>45</v>
       </c>
       <c r="L86" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-8</v>
       </c>
       <c r="M86" s="1"/>
@@ -15314,12 +15554,12 @@
         <v>300</v>
       </c>
       <c r="P86" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>7.4</v>
       </c>
       <c r="Q86" s="5"/>
       <c r="R86" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>150</v>
       </c>
       <c r="S86" s="22">
@@ -15327,11 +15567,11 @@
         <v>150</v>
       </c>
       <c r="T86" s="1">
+        <f t="shared" si="25"/>
+        <v>61.756756756756751</v>
+      </c>
+      <c r="U86" s="1">
         <f t="shared" si="24"/>
-        <v>61.756756756756751</v>
-      </c>
-      <c r="U86" s="1">
-        <f t="shared" si="23"/>
         <v>41.486486486486484</v>
       </c>
       <c r="V86" s="1">
@@ -15368,10 +15608,13 @@
         <v>140</v>
       </c>
       <c r="AG86" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>61.499999999999993</v>
       </c>
-      <c r="AH86" s="20"/>
+      <c r="AH86" s="20">
+        <f t="shared" si="27"/>
+        <v>3.0339999999999998</v>
+      </c>
       <c r="AI86" s="1"/>
       <c r="AJ86" s="1"/>
       <c r="AK86" s="1"/>
@@ -15414,7 +15657,7 @@
       <c r="J87" s="11"/>
       <c r="K87" s="11"/>
       <c r="L87" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M87" s="11"/>
@@ -15423,7 +15666,7 @@
         <v>0</v>
       </c>
       <c r="P87" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="Q87" s="14"/>
@@ -15433,13 +15676,13 @@
         <v>50</v>
       </c>
       <c r="T87" s="1" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U87" s="11" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U87" s="11" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="V87" s="11">
         <v>0</v>
       </c>
@@ -15472,10 +15715,13 @@
       </c>
       <c r="AF87" s="11"/>
       <c r="AG87" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AH87" s="20"/>
+      <c r="AH87" s="20">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
       <c r="AI87" s="1"/>
       <c r="AJ87" s="1"/>
       <c r="AK87" s="1"/>
@@ -15526,7 +15772,7 @@
         <v>53</v>
       </c>
       <c r="L88" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-5</v>
       </c>
       <c r="M88" s="1"/>
@@ -15535,61 +15781,64 @@
         <v>0</v>
       </c>
       <c r="P88" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>9.6</v>
       </c>
       <c r="Q88" s="5"/>
       <c r="R88" s="5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="S88" s="22"/>
+      <c r="T88" s="1">
+        <f t="shared" si="25"/>
+        <v>22.5</v>
+      </c>
+      <c r="U88" s="1">
+        <f t="shared" si="24"/>
+        <v>22.5</v>
+      </c>
+      <c r="V88" s="1">
+        <v>5</v>
+      </c>
+      <c r="W88" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="X88" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="Y88" s="1">
+        <v>16.2</v>
+      </c>
+      <c r="Z88" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA88" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="AG88" s="1">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="S88" s="22"/>
-      <c r="T88" s="1">
-        <f t="shared" si="24"/>
-        <v>22.5</v>
-      </c>
-      <c r="U88" s="1">
-        <f t="shared" si="23"/>
-        <v>22.5</v>
-      </c>
-      <c r="V88" s="1">
-        <v>5</v>
-      </c>
-      <c r="W88" s="1">
-        <v>6.2</v>
-      </c>
-      <c r="X88" s="1">
-        <v>2.8</v>
-      </c>
-      <c r="Y88" s="1">
-        <v>16.2</v>
-      </c>
-      <c r="Z88" s="1">
-        <v>2</v>
-      </c>
-      <c r="AA88" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB88" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC88" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD88" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE88" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF88" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="AG88" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AH88" s="20"/>
+      <c r="AH88" s="20">
+        <f t="shared" si="27"/>
+        <v>2.496</v>
+      </c>
       <c r="AI88" s="1"/>
       <c r="AJ88" s="1"/>
       <c r="AK88" s="1"/>
@@ -15638,7 +15887,7 @@
         <v>6.5</v>
       </c>
       <c r="L89" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>3.4879999999999995</v>
       </c>
       <c r="M89" s="1"/>
@@ -15647,7 +15896,7 @@
         <v>0</v>
       </c>
       <c r="P89" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1.9975999999999998</v>
       </c>
       <c r="Q89" s="5">
@@ -15655,56 +15904,59 @@
         <v>12.684399999999997</v>
       </c>
       <c r="R89" s="5">
+        <f t="shared" si="28"/>
+        <v>13</v>
+      </c>
+      <c r="S89" s="22"/>
+      <c r="T89" s="1">
+        <f t="shared" si="25"/>
+        <v>14.157989587505007</v>
+      </c>
+      <c r="U89" s="1">
+        <f t="shared" si="24"/>
+        <v>7.6501802162595123</v>
+      </c>
+      <c r="V89" s="1">
+        <v>1.3373999999999999</v>
+      </c>
+      <c r="W89" s="1">
+        <v>3.1549999999999998</v>
+      </c>
+      <c r="X89" s="1">
+        <v>6.3369999999999997</v>
+      </c>
+      <c r="Y89" s="1">
+        <v>10.9542</v>
+      </c>
+      <c r="Z89" s="1">
+        <v>1.6482000000000001</v>
+      </c>
+      <c r="AA89" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="AG89" s="1">
         <f t="shared" si="26"/>
         <v>13</v>
       </c>
-      <c r="S89" s="22"/>
-      <c r="T89" s="1">
-        <f t="shared" si="24"/>
-        <v>14.157989587505007</v>
-      </c>
-      <c r="U89" s="1">
-        <f t="shared" si="23"/>
-        <v>7.6501802162595123</v>
-      </c>
-      <c r="V89" s="1">
-        <v>1.3373999999999999</v>
-      </c>
-      <c r="W89" s="1">
-        <v>3.1549999999999998</v>
-      </c>
-      <c r="X89" s="1">
-        <v>6.3369999999999997</v>
-      </c>
-      <c r="Y89" s="1">
-        <v>10.9542</v>
-      </c>
-      <c r="Z89" s="1">
-        <v>1.6482000000000001</v>
-      </c>
-      <c r="AA89" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC89" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD89" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE89" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF89" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="AG89" s="1">
-        <f t="shared" si="25"/>
-        <v>13</v>
-      </c>
-      <c r="AH89" s="20"/>
+      <c r="AH89" s="20">
+        <f t="shared" si="27"/>
+        <v>1.9975999999999998</v>
+      </c>
       <c r="AI89" s="1"/>
       <c r="AJ89" s="1"/>
       <c r="AK89" s="1"/>
@@ -15755,7 +16007,7 @@
         <v>21</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-5</v>
       </c>
       <c r="M90" s="1"/>
@@ -15764,61 +16016,64 @@
         <v>0</v>
       </c>
       <c r="P90" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>3.2</v>
       </c>
       <c r="Q90" s="5"/>
       <c r="R90" s="5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="S90" s="22"/>
+      <c r="T90" s="1">
+        <f t="shared" si="25"/>
+        <v>30.9375</v>
+      </c>
+      <c r="U90" s="1">
+        <f t="shared" si="24"/>
+        <v>30.9375</v>
+      </c>
+      <c r="V90" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="W90" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="X90" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="Y90" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="Z90" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="AA90" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB90" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC90" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD90" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF90" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="AG90" s="1">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="S90" s="22"/>
-      <c r="T90" s="1">
-        <f t="shared" si="24"/>
-        <v>30.9375</v>
-      </c>
-      <c r="U90" s="1">
-        <f t="shared" si="23"/>
-        <v>30.9375</v>
-      </c>
-      <c r="V90" s="1">
-        <v>2.8</v>
-      </c>
-      <c r="W90" s="1">
-        <v>2.4</v>
-      </c>
-      <c r="X90" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="Y90" s="1">
-        <v>7.4</v>
-      </c>
-      <c r="Z90" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="AA90" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB90" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC90" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD90" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE90" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF90" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="AG90" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AH90" s="20"/>
+      <c r="AH90" s="20">
+        <f t="shared" si="27"/>
+        <v>0.99199999999999999</v>
+      </c>
       <c r="AI90" s="1"/>
       <c r="AJ90" s="1"/>
       <c r="AK90" s="1"/>
@@ -15869,7 +16124,7 @@
         <v>3.7</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.66300000000000026</v>
       </c>
       <c r="M91" s="1"/>
@@ -15878,61 +16133,64 @@
         <v>0</v>
       </c>
       <c r="P91" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.87260000000000004</v>
       </c>
       <c r="Q91" s="5"/>
       <c r="R91" s="5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="S91" s="22"/>
+      <c r="T91" s="1">
+        <f t="shared" si="25"/>
+        <v>35.143250057300023</v>
+      </c>
+      <c r="U91" s="1">
+        <f t="shared" si="24"/>
+        <v>35.143250057300023</v>
+      </c>
+      <c r="V91" s="1">
+        <v>1.1374</v>
+      </c>
+      <c r="W91" s="1">
+        <v>0</v>
+      </c>
+      <c r="X91" s="1">
+        <v>0.83539999999999992</v>
+      </c>
+      <c r="Y91" s="1">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="Z91" s="1">
+        <v>0.94100000000000006</v>
+      </c>
+      <c r="AA91" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="AG91" s="1">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="S91" s="22"/>
-      <c r="T91" s="1">
-        <f t="shared" si="24"/>
-        <v>35.143250057300023</v>
-      </c>
-      <c r="U91" s="1">
-        <f t="shared" si="23"/>
-        <v>35.143250057300023</v>
-      </c>
-      <c r="V91" s="1">
-        <v>1.1374</v>
-      </c>
-      <c r="W91" s="1">
-        <v>0</v>
-      </c>
-      <c r="X91" s="1">
-        <v>0.83539999999999992</v>
-      </c>
-      <c r="Y91" s="1">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="Z91" s="1">
-        <v>0.94100000000000006</v>
-      </c>
-      <c r="AA91" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC91" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD91" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE91" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF91" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AG91" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AH91" s="20"/>
+      <c r="AH91" s="20">
+        <f t="shared" si="27"/>
+        <v>0.87260000000000004</v>
+      </c>
       <c r="AI91" s="1"/>
       <c r="AJ91" s="1"/>
       <c r="AK91" s="1"/>
@@ -15983,7 +16241,7 @@
         <v>19</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-6</v>
       </c>
       <c r="M92" s="1"/>
@@ -15992,59 +16250,62 @@
         <v>39</v>
       </c>
       <c r="P92" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2.6</v>
       </c>
       <c r="Q92" s="5"/>
       <c r="R92" s="5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="S92" s="22"/>
+      <c r="T92" s="1">
+        <f t="shared" si="25"/>
+        <v>30.769230769230766</v>
+      </c>
+      <c r="U92" s="1">
+        <f t="shared" si="24"/>
+        <v>30.769230769230766</v>
+      </c>
+      <c r="V92" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="W92" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="X92" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="Y92" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="1">
+        <v>11.4</v>
+      </c>
+      <c r="AA92" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB92" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="AC92" s="1">
+        <v>10</v>
+      </c>
+      <c r="AD92" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="AE92" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="AF92" s="1"/>
+      <c r="AG92" s="1">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="S92" s="22"/>
-      <c r="T92" s="1">
-        <f t="shared" si="24"/>
-        <v>30.769230769230766</v>
-      </c>
-      <c r="U92" s="1">
-        <f t="shared" si="23"/>
-        <v>30.769230769230766</v>
-      </c>
-      <c r="V92" s="1">
-        <v>7.6</v>
-      </c>
-      <c r="W92" s="1">
-        <v>8.6</v>
-      </c>
-      <c r="X92" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="Y92" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z92" s="1">
-        <v>11.4</v>
-      </c>
-      <c r="AA92" s="1">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="AB92" s="1">
-        <v>2.4</v>
-      </c>
-      <c r="AC92" s="1">
-        <v>10</v>
-      </c>
-      <c r="AD92" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="AE92" s="1">
-        <v>5.2</v>
-      </c>
-      <c r="AF92" s="1"/>
-      <c r="AG92" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AH92" s="20"/>
+      <c r="AH92" s="20">
+        <f t="shared" si="27"/>
+        <v>1.04</v>
+      </c>
       <c r="AI92" s="1"/>
       <c r="AJ92" s="1"/>
       <c r="AK92" s="1"/>
@@ -16095,7 +16356,7 @@
         <v>59</v>
       </c>
       <c r="L93" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-8</v>
       </c>
       <c r="M93" s="1"/>
@@ -16104,7 +16365,7 @@
         <v>25</v>
       </c>
       <c r="P93" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>10.199999999999999</v>
       </c>
       <c r="Q93" s="5">
@@ -16119,11 +16380,11 @@
         <v>150</v>
       </c>
       <c r="T93" s="1">
+        <f t="shared" si="25"/>
+        <v>17.254901960784316</v>
+      </c>
+      <c r="U93" s="1">
         <f t="shared" si="24"/>
-        <v>17.254901960784316</v>
-      </c>
-      <c r="U93" s="1">
-        <f t="shared" si="23"/>
         <v>4.5098039215686274</v>
       </c>
       <c r="V93" s="1">
@@ -16158,10 +16419,13 @@
       </c>
       <c r="AF93" s="1"/>
       <c r="AG93" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>45.5</v>
       </c>
-      <c r="AH93" s="20"/>
+      <c r="AH93" s="20">
+        <f t="shared" si="27"/>
+        <v>3.5699999999999994</v>
+      </c>
       <c r="AI93" s="1"/>
       <c r="AJ93" s="1"/>
       <c r="AK93" s="1"/>
@@ -16204,7 +16468,7 @@
         <v>1</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-1</v>
       </c>
       <c r="M94" s="1"/>
@@ -16213,64 +16477,67 @@
         <v>0</v>
       </c>
       <c r="P94" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="Q94" s="18">
-        <f t="shared" ref="Q94" si="29">15*P94-O94-F94</f>
+        <f t="shared" ref="Q94" si="31">15*P94-O94-F94</f>
         <v>0</v>
       </c>
       <c r="R94" s="5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="S94" s="22"/>
+      <c r="T94" s="1" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U94" s="1" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V94" s="1">
+        <v>0</v>
+      </c>
+      <c r="W94" s="1">
+        <v>0.4284</v>
+      </c>
+      <c r="X94" s="1">
+        <v>1.5244</v>
+      </c>
+      <c r="Y94" s="1">
+        <v>0.72140000000000004</v>
+      </c>
+      <c r="Z94" s="1">
+        <v>0.48580000000000001</v>
+      </c>
+      <c r="AA94" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="AG94" s="1">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="S94" s="22"/>
-      <c r="T94" s="1" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U94" s="1" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V94" s="1">
+      <c r="AH94" s="20">
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="W94" s="1">
-        <v>0.4284</v>
-      </c>
-      <c r="X94" s="1">
-        <v>1.5244</v>
-      </c>
-      <c r="Y94" s="1">
-        <v>0.72140000000000004</v>
-      </c>
-      <c r="Z94" s="1">
-        <v>0.48580000000000001</v>
-      </c>
-      <c r="AA94" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC94" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD94" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE94" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="AG94" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AH94" s="20"/>
       <c r="AI94" s="1"/>
       <c r="AJ94" s="1"/>
       <c r="AK94" s="1"/>
@@ -16319,7 +16586,7 @@
         <v>14.8</v>
       </c>
       <c r="L95" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-4.6070000000000011</v>
       </c>
       <c r="M95" s="1"/>
@@ -16328,7 +16595,7 @@
         <v>24</v>
       </c>
       <c r="P95" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2.0385999999999997</v>
       </c>
       <c r="Q95" s="5"/>
@@ -16340,11 +16607,11 @@
         <v>100</v>
       </c>
       <c r="T95" s="1">
+        <f t="shared" si="25"/>
+        <v>24.553124693417054</v>
+      </c>
+      <c r="U95" s="1">
         <f t="shared" si="24"/>
-        <v>24.553124693417054</v>
-      </c>
-      <c r="U95" s="1">
-        <f t="shared" si="23"/>
         <v>16.704601196899837</v>
       </c>
       <c r="V95" s="1">
@@ -16379,10 +16646,13 @@
       </c>
       <c r="AF95" s="1"/>
       <c r="AG95" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>16</v>
       </c>
-      <c r="AH95" s="20"/>
+      <c r="AH95" s="20">
+        <f t="shared" si="27"/>
+        <v>2.0385999999999997</v>
+      </c>
       <c r="AI95" s="1"/>
       <c r="AJ95" s="1"/>
       <c r="AK95" s="1"/>
@@ -16433,7 +16703,7 @@
         <v>150</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-128</v>
       </c>
       <c r="M96" s="1"/>
@@ -16442,59 +16712,62 @@
         <v>157</v>
       </c>
       <c r="P96" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="Q96" s="5"/>
       <c r="R96" s="5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="S96" s="22"/>
+      <c r="T96" s="1">
+        <f t="shared" si="25"/>
+        <v>36.36363636363636</v>
+      </c>
+      <c r="U96" s="1">
+        <f t="shared" si="24"/>
+        <v>36.36363636363636</v>
+      </c>
+      <c r="V96" s="1">
+        <v>19.8</v>
+      </c>
+      <c r="W96" s="1">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="X96" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="Y96" s="1">
+        <v>13.2</v>
+      </c>
+      <c r="Z96" s="1">
+        <v>13.6</v>
+      </c>
+      <c r="AA96" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="AB96" s="1">
+        <v>25.6</v>
+      </c>
+      <c r="AC96" s="1">
+        <v>21.6</v>
+      </c>
+      <c r="AD96" s="1">
+        <v>4</v>
+      </c>
+      <c r="AE96" s="1">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="AF96" s="1"/>
+      <c r="AG96" s="1">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="S96" s="22"/>
-      <c r="T96" s="1">
-        <f t="shared" si="24"/>
-        <v>36.36363636363636</v>
-      </c>
-      <c r="U96" s="1">
-        <f t="shared" si="23"/>
-        <v>36.36363636363636</v>
-      </c>
-      <c r="V96" s="1">
-        <v>19.8</v>
-      </c>
-      <c r="W96" s="1">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="X96" s="1">
-        <v>6.8</v>
-      </c>
-      <c r="Y96" s="1">
-        <v>13.2</v>
-      </c>
-      <c r="Z96" s="1">
-        <v>13.6</v>
-      </c>
-      <c r="AA96" s="1">
-        <v>6.8</v>
-      </c>
-      <c r="AB96" s="1">
-        <v>25.6</v>
-      </c>
-      <c r="AC96" s="1">
-        <v>21.6</v>
-      </c>
-      <c r="AD96" s="1">
-        <v>4</v>
-      </c>
-      <c r="AE96" s="1">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="AF96" s="1"/>
-      <c r="AG96" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AH96" s="20"/>
+      <c r="AH96" s="20">
+        <f t="shared" si="27"/>
+        <v>1.4520000000000002</v>
+      </c>
       <c r="AI96" s="1"/>
       <c r="AJ96" s="1"/>
       <c r="AK96" s="1"/>
@@ -16543,7 +16816,7 @@
         <v>216</v>
       </c>
       <c r="L97" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-24</v>
       </c>
       <c r="M97" s="1"/>
@@ -16552,7 +16825,7 @@
         <v>41</v>
       </c>
       <c r="P97" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>38.4</v>
       </c>
       <c r="Q97" s="5">
@@ -16560,7 +16833,7 @@
         <v>343.4</v>
       </c>
       <c r="R97" s="5">
-        <f t="shared" ref="R97:R98" si="30">S97</f>
+        <f t="shared" ref="R97:R98" si="32">S97</f>
         <v>600</v>
       </c>
       <c r="S97" s="22">
@@ -16568,11 +16841,11 @@
         <v>600</v>
       </c>
       <c r="T97" s="1">
+        <f t="shared" si="25"/>
+        <v>17.682291666666668</v>
+      </c>
+      <c r="U97" s="1">
         <f t="shared" si="24"/>
-        <v>17.682291666666668</v>
-      </c>
-      <c r="U97" s="1">
-        <f t="shared" si="23"/>
         <v>2.057291666666667</v>
       </c>
       <c r="V97" s="1">
@@ -16607,10 +16880,13 @@
       </c>
       <c r="AF97" s="1"/>
       <c r="AG97" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>60</v>
       </c>
-      <c r="AH97" s="20"/>
+      <c r="AH97" s="20">
+        <f t="shared" si="27"/>
+        <v>3.84</v>
+      </c>
       <c r="AI97" s="1"/>
       <c r="AJ97" s="1"/>
       <c r="AK97" s="1"/>
@@ -16661,7 +16937,7 @@
         <v>114</v>
       </c>
       <c r="L98" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-31</v>
       </c>
       <c r="M98" s="1"/>
@@ -16670,7 +16946,7 @@
         <v>26</v>
       </c>
       <c r="P98" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>16.600000000000001</v>
       </c>
       <c r="Q98" s="5">
@@ -16678,7 +16954,7 @@
         <v>154.80000000000001</v>
       </c>
       <c r="R98" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>200</v>
       </c>
       <c r="S98" s="22">
@@ -16686,11 +16962,11 @@
         <v>200</v>
       </c>
       <c r="T98" s="1">
+        <f t="shared" si="25"/>
+        <v>15.722891566265059</v>
+      </c>
+      <c r="U98" s="1">
         <f t="shared" si="24"/>
-        <v>15.722891566265059</v>
-      </c>
-      <c r="U98" s="1">
-        <f t="shared" si="23"/>
         <v>3.6746987951807224</v>
       </c>
       <c r="V98" s="1">
@@ -16727,10 +17003,13 @@
         <v>154</v>
       </c>
       <c r="AG98" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>20</v>
       </c>
-      <c r="AH98" s="20"/>
+      <c r="AH98" s="20">
+        <f t="shared" si="27"/>
+        <v>1.6600000000000001</v>
+      </c>
       <c r="AI98" s="1"/>
       <c r="AJ98" s="1"/>
       <c r="AK98" s="1"/>
@@ -16777,7 +17056,7 @@
         <v>92</v>
       </c>
       <c r="L99" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-91</v>
       </c>
       <c r="M99" s="1"/>
@@ -16786,59 +17065,62 @@
         <v>220</v>
       </c>
       <c r="P99" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.2</v>
       </c>
       <c r="Q99" s="5"/>
       <c r="R99" s="5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="S99" s="22"/>
+      <c r="T99" s="1">
+        <f t="shared" si="25"/>
+        <v>1100</v>
+      </c>
+      <c r="U99" s="1">
+        <f t="shared" si="24"/>
+        <v>1100</v>
+      </c>
+      <c r="V99" s="1">
+        <v>22.6</v>
+      </c>
+      <c r="W99" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="X99" s="1">
+        <v>9.6</v>
+      </c>
+      <c r="Y99" s="1">
+        <v>19</v>
+      </c>
+      <c r="Z99" s="1">
+        <v>11.2</v>
+      </c>
+      <c r="AA99" s="1">
+        <v>11</v>
+      </c>
+      <c r="AB99" s="1">
+        <v>11.8</v>
+      </c>
+      <c r="AC99" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="AD99" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="AE99" s="1">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="AF99" s="1"/>
+      <c r="AG99" s="1">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="S99" s="22"/>
-      <c r="T99" s="1">
-        <f t="shared" si="24"/>
-        <v>1100</v>
-      </c>
-      <c r="U99" s="1">
-        <f t="shared" si="23"/>
-        <v>1100</v>
-      </c>
-      <c r="V99" s="1">
-        <v>22.6</v>
-      </c>
-      <c r="W99" s="1">
-        <v>7.4</v>
-      </c>
-      <c r="X99" s="1">
-        <v>9.6</v>
-      </c>
-      <c r="Y99" s="1">
-        <v>19</v>
-      </c>
-      <c r="Z99" s="1">
-        <v>11.2</v>
-      </c>
-      <c r="AA99" s="1">
-        <v>11</v>
-      </c>
-      <c r="AB99" s="1">
-        <v>11.8</v>
-      </c>
-      <c r="AC99" s="1">
-        <v>7.6</v>
-      </c>
-      <c r="AD99" s="1">
-        <v>30.8</v>
-      </c>
-      <c r="AE99" s="1">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="AF99" s="1"/>
-      <c r="AG99" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AH99" s="20"/>
+      <c r="AH99" s="20">
+        <f t="shared" si="27"/>
+        <v>8.0000000000000016E-2</v>
+      </c>
       <c r="AI99" s="1"/>
       <c r="AJ99" s="1"/>
       <c r="AK99" s="1"/>
@@ -16885,7 +17167,7 @@
         <v>5</v>
       </c>
       <c r="L100" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M100" s="11"/>
@@ -16894,61 +17176,64 @@
         <v>0</v>
       </c>
       <c r="P100" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="Q100" s="14"/>
       <c r="R100" s="5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="S100" s="22"/>
+      <c r="T100" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="U100" s="11">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="V100" s="11">
+        <v>0.6</v>
+      </c>
+      <c r="W100" s="11">
+        <v>0</v>
+      </c>
+      <c r="X100" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="11">
+        <v>-0.2</v>
+      </c>
+      <c r="Z100" s="11">
+        <v>0.6</v>
+      </c>
+      <c r="AA100" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="AB100" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="AD100" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="AE100" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AF100" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="AG100" s="1">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="S100" s="22"/>
-      <c r="T100" s="1">
-        <f t="shared" si="24"/>
+      <c r="AH100" s="20">
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="U100" s="11">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="V100" s="11">
-        <v>0.6</v>
-      </c>
-      <c r="W100" s="11">
-        <v>0</v>
-      </c>
-      <c r="X100" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="11">
-        <v>-0.2</v>
-      </c>
-      <c r="Z100" s="11">
-        <v>0.6</v>
-      </c>
-      <c r="AA100" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="AB100" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="AD100" s="11">
-        <v>2.4</v>
-      </c>
-      <c r="AE100" s="11">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="AF100" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="AG100" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AH100" s="20"/>
       <c r="AI100" s="1"/>
       <c r="AJ100" s="1"/>
       <c r="AK100" s="1"/>
@@ -16997,7 +17282,7 @@
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
       <c r="L101" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-0.51100000000000001</v>
       </c>
       <c r="M101" s="1"/>
@@ -17007,61 +17292,64 @@
         <v>45</v>
       </c>
       <c r="P101" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-0.1022</v>
       </c>
       <c r="Q101" s="5"/>
       <c r="R101" s="5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="S101" s="22"/>
+      <c r="T101" s="1">
+        <f t="shared" si="25"/>
+        <v>-617.66144814090023</v>
+      </c>
+      <c r="U101" s="1">
+        <f t="shared" si="24"/>
+        <v>-617.66144814090023</v>
+      </c>
+      <c r="V101" s="1">
+        <v>0</v>
+      </c>
+      <c r="W101" s="1">
+        <v>0</v>
+      </c>
+      <c r="X101" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="AG101" s="1">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="S101" s="22"/>
-      <c r="T101" s="1">
-        <f t="shared" si="24"/>
-        <v>-617.66144814090023</v>
-      </c>
-      <c r="U101" s="1">
-        <f t="shared" si="23"/>
-        <v>-617.66144814090023</v>
-      </c>
-      <c r="V101" s="1">
-        <v>0</v>
-      </c>
-      <c r="W101" s="1">
-        <v>0</v>
-      </c>
-      <c r="X101" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA101" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC101" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD101" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF101" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="AG101" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AH101" s="20"/>
+      <c r="AH101" s="20">
+        <f t="shared" si="27"/>
+        <v>-0.1022</v>
+      </c>
       <c r="AI101" s="1"/>
       <c r="AJ101" s="1"/>
       <c r="AK101" s="1"/>
@@ -17112,7 +17400,7 @@
         <v>7</v>
       </c>
       <c r="L102" s="1">
-        <f t="shared" ref="L102:L107" si="31">E102-K102</f>
+        <f t="shared" ref="L102:L107" si="33">E102-K102</f>
         <v>-3</v>
       </c>
       <c r="M102" s="1"/>
@@ -17121,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="P102" s="1">
-        <f t="shared" ref="P102:P107" si="32">E102/5</f>
+        <f t="shared" ref="P102:P107" si="34">E102/5</f>
         <v>0.8</v>
       </c>
       <c r="Q102" s="5">
@@ -17135,11 +17423,11 @@
         <v>100</v>
       </c>
       <c r="T102" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>53.75</v>
       </c>
       <c r="U102" s="1">
-        <f t="shared" ref="U102:U107" si="33">(F102+O102)/P102</f>
+        <f t="shared" ref="U102:U107" si="35">(F102+O102)/P102</f>
         <v>-8.75</v>
       </c>
       <c r="V102" s="1">
@@ -17176,10 +17464,13 @@
         <v>172</v>
       </c>
       <c r="AG102" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>15</v>
       </c>
-      <c r="AH102" s="20"/>
+      <c r="AH102" s="20">
+        <f t="shared" si="27"/>
+        <v>0.24</v>
+      </c>
       <c r="AI102" s="1"/>
       <c r="AJ102" s="1"/>
       <c r="AK102" s="1"/>
@@ -17228,7 +17519,7 @@
         <v>9</v>
       </c>
       <c r="L103" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M103" s="1"/>
@@ -17237,7 +17528,7 @@
         <v>0</v>
       </c>
       <c r="P103" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1.8</v>
       </c>
       <c r="Q103" s="5"/>
@@ -17249,11 +17540,11 @@
         <v>70</v>
       </c>
       <c r="T103" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>25</v>
       </c>
       <c r="U103" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>19.444444444444443</v>
       </c>
       <c r="V103" s="1">
@@ -17290,10 +17581,13 @@
         <v>170</v>
       </c>
       <c r="AG103" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
-      <c r="AH103" s="20"/>
+      <c r="AH103" s="20">
+        <f t="shared" si="27"/>
+        <v>0.18000000000000002</v>
+      </c>
       <c r="AI103" s="1"/>
       <c r="AJ103" s="1"/>
       <c r="AK103" s="1"/>
@@ -17345,7 +17639,7 @@
         <v>7</v>
       </c>
       <c r="L104" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>2</v>
       </c>
       <c r="M104" s="1"/>
@@ -17354,7 +17648,7 @@
         <v>0</v>
       </c>
       <c r="P104" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1.8</v>
       </c>
       <c r="Q104" s="5"/>
@@ -17366,11 +17660,11 @@
         <v>70</v>
       </c>
       <c r="T104" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>27.777777777777779</v>
       </c>
       <c r="U104" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>22.222222222222221</v>
       </c>
       <c r="V104" s="1">
@@ -17407,10 +17701,13 @@
         <v>171</v>
       </c>
       <c r="AG104" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
-      <c r="AH104" s="20"/>
+      <c r="AH104" s="20">
+        <f t="shared" si="27"/>
+        <v>0.18000000000000002</v>
+      </c>
       <c r="AI104" s="1"/>
       <c r="AJ104" s="1"/>
       <c r="AK104" s="1"/>
@@ -17456,68 +17753,71 @@
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
       <c r="L105" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M105" s="1"/>
       <c r="N105" s="1"/>
       <c r="O105" s="1"/>
       <c r="P105" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Q105" s="5"/>
       <c r="R105" s="5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="S105" s="22"/>
+      <c r="T105" s="1" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U105" s="1" t="e">
+        <f t="shared" si="35"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V105" s="1">
+        <v>0</v>
+      </c>
+      <c r="W105" s="1">
+        <v>0</v>
+      </c>
+      <c r="X105" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z105" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA105" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB105" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC105" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD105" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE105" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF105" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="AG105" s="1">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="S105" s="22"/>
-      <c r="T105" s="1" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U105" s="1" t="e">
-        <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V105" s="1">
+      <c r="AH105" s="20">
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="W105" s="1">
-        <v>0</v>
-      </c>
-      <c r="X105" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y105" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z105" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA105" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB105" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC105" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD105" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE105" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF105" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="AG105" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AH105" s="20"/>
       <c r="AI105" s="1"/>
       <c r="AJ105" s="1"/>
       <c r="AK105" s="1"/>
@@ -17558,7 +17858,7 @@
       <c r="J106" s="11"/>
       <c r="K106" s="11"/>
       <c r="L106" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M106" s="11"/>
@@ -17567,61 +17867,64 @@
         <v>0</v>
       </c>
       <c r="P106" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Q106" s="14"/>
       <c r="R106" s="5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="S106" s="22"/>
+      <c r="T106" s="1" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U106" s="11" t="e">
+        <f t="shared" si="35"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V106" s="11">
+        <v>0</v>
+      </c>
+      <c r="W106" s="11">
+        <v>0</v>
+      </c>
+      <c r="X106" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y106" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z106" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA106" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB106" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC106" s="11">
+        <v>0</v>
+      </c>
+      <c r="AD106" s="11">
+        <v>0</v>
+      </c>
+      <c r="AE106" s="11">
+        <v>0</v>
+      </c>
+      <c r="AF106" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG106" s="1">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="S106" s="22"/>
-      <c r="T106" s="1" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U106" s="11" t="e">
-        <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V106" s="11">
+      <c r="AH106" s="20">
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="W106" s="11">
-        <v>0</v>
-      </c>
-      <c r="X106" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y106" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z106" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA106" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB106" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC106" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD106" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE106" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF106" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="AG106" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AH106" s="20"/>
       <c r="AI106" s="1"/>
       <c r="AJ106" s="1"/>
       <c r="AK106" s="1"/>
@@ -17666,7 +17969,7 @@
       </c>
       <c r="K107" s="11"/>
       <c r="L107" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M107" s="11"/>
@@ -17675,59 +17978,62 @@
         <v>0</v>
       </c>
       <c r="P107" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Q107" s="14"/>
       <c r="R107" s="5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="S107" s="22"/>
+      <c r="T107" s="1" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U107" s="11" t="e">
+        <f t="shared" si="35"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V107" s="11">
+        <v>0</v>
+      </c>
+      <c r="W107" s="11">
+        <v>0</v>
+      </c>
+      <c r="X107" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB107" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC107" s="11">
+        <v>0</v>
+      </c>
+      <c r="AD107" s="11">
+        <v>1.4</v>
+      </c>
+      <c r="AE107" s="11">
+        <v>0</v>
+      </c>
+      <c r="AF107" s="11"/>
+      <c r="AG107" s="1">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="S107" s="22"/>
-      <c r="T107" s="1" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U107" s="11" t="e">
-        <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V107" s="11">
+      <c r="AH107" s="20">
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="W107" s="11">
-        <v>0</v>
-      </c>
-      <c r="X107" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y107" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z107" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA107" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB107" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC107" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD107" s="11">
-        <v>1.4</v>
-      </c>
-      <c r="AE107" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF107" s="11"/>
-      <c r="AG107" s="1">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AH107" s="20"/>
       <c r="AI107" s="1"/>
       <c r="AJ107" s="1"/>
       <c r="AK107" s="1"/>
